--- a/data/WP18_sachgebiete_AfD.xlsx
+++ b/data/WP18_sachgebiete_AfD.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="152">
   <si>
     <t xml:space="preserve">Sachgebiet</t>
   </si>
@@ -27,9 +27,6 @@
   </si>
   <si>
     <t xml:space="preserve">Verspätet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pünktlichkeitsquote</t>
   </si>
   <si>
     <t xml:space="preserve">Innere Sicherheit</t>
@@ -815,13 +812,10 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2" t="n">
         <v>18</v>
@@ -835,13 +829,10 @@
       <c r="E2" t="n">
         <v>1123</v>
       </c>
-      <c r="F2" t="n">
-        <v>21.6875871687587</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3" t="n">
         <v>18</v>
@@ -855,13 +846,10 @@
       <c r="E3" t="n">
         <v>498</v>
       </c>
-      <c r="F3" t="n">
-        <v>17.1381031613977</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4" t="n">
         <v>18</v>
@@ -875,13 +863,10 @@
       <c r="E4" t="n">
         <v>303</v>
       </c>
-      <c r="F4" t="n">
-        <v>12.9310344827586</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" t="n">
         <v>18</v>
@@ -895,13 +880,10 @@
       <c r="E5" t="n">
         <v>207</v>
       </c>
-      <c r="F5" t="n">
-        <v>14.1078838174274</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" t="n">
         <v>18</v>
@@ -915,13 +897,10 @@
       <c r="E6" t="n">
         <v>165</v>
       </c>
-      <c r="F6" t="n">
-        <v>22.5352112676056</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7" t="n">
         <v>18</v>
@@ -935,13 +914,10 @@
       <c r="E7" t="n">
         <v>143</v>
       </c>
-      <c r="F7" t="n">
-        <v>10.062893081761</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8" t="n">
         <v>18</v>
@@ -955,13 +931,10 @@
       <c r="E8" t="n">
         <v>125</v>
       </c>
-      <c r="F8" t="n">
-        <v>18.3006535947712</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>18</v>
@@ -975,13 +948,10 @@
       <c r="E9" t="n">
         <v>124</v>
       </c>
-      <c r="F9" t="n">
-        <v>18.9542483660131</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B10" t="n">
         <v>18</v>
@@ -995,13 +965,10 @@
       <c r="E10" t="n">
         <v>67</v>
       </c>
-      <c r="F10" t="n">
-        <v>54.1095890410959</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B11" t="n">
         <v>18</v>
@@ -1015,13 +982,10 @@
       <c r="E11" t="n">
         <v>113</v>
       </c>
-      <c r="F11" t="n">
-        <v>20.4225352112676</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B12" t="n">
         <v>18</v>
@@ -1035,13 +999,10 @@
       <c r="E12" t="n">
         <v>85</v>
       </c>
-      <c r="F12" t="n">
-        <v>11.4583333333333</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B13" t="n">
         <v>18</v>
@@ -1055,13 +1016,10 @@
       <c r="E13" t="n">
         <v>71</v>
       </c>
-      <c r="F13" t="n">
-        <v>12.3456790123457</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" t="n">
         <v>18</v>
@@ -1075,13 +1033,10 @@
       <c r="E14" t="n">
         <v>56</v>
       </c>
-      <c r="F14" t="n">
-        <v>26.3157894736842</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B15" t="n">
         <v>18</v>
@@ -1095,13 +1050,10 @@
       <c r="E15" t="n">
         <v>55</v>
       </c>
-      <c r="F15" t="n">
-        <v>26.6666666666667</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B16" t="n">
         <v>18</v>
@@ -1115,13 +1067,10 @@
       <c r="E16" t="n">
         <v>52</v>
       </c>
-      <c r="F16" t="n">
-        <v>25.7142857142857</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B17" t="n">
         <v>18</v>
@@ -1135,13 +1084,10 @@
       <c r="E17" t="n">
         <v>65</v>
       </c>
-      <c r="F17" t="n">
-        <v>1.51515151515152</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B18" t="n">
         <v>18</v>
@@ -1155,13 +1101,10 @@
       <c r="E18" t="n">
         <v>60</v>
       </c>
-      <c r="F18" t="n">
-        <v>4.76190476190477</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B19" t="n">
         <v>18</v>
@@ -1175,13 +1118,10 @@
       <c r="E19" t="n">
         <v>60</v>
       </c>
-      <c r="F19" t="n">
-        <v>3.2258064516129</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B20" t="n">
         <v>18</v>
@@ -1195,13 +1135,10 @@
       <c r="E20" t="n">
         <v>49</v>
       </c>
-      <c r="F20" t="n">
-        <v>20.9677419354839</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B21" t="n">
         <v>18</v>
@@ -1215,13 +1152,10 @@
       <c r="E21" t="n">
         <v>38</v>
       </c>
-      <c r="F21" t="n">
-        <v>28.3018867924528</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B22" t="n">
         <v>18</v>
@@ -1235,13 +1169,10 @@
       <c r="E22" t="n">
         <v>38</v>
       </c>
-      <c r="F22" t="n">
-        <v>28.3018867924528</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B23" t="n">
         <v>18</v>
@@ -1255,13 +1186,10 @@
       <c r="E23" t="n">
         <v>34</v>
       </c>
-      <c r="F23" t="n">
-        <v>34.6153846153846</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B24" t="n">
         <v>18</v>
@@ -1275,13 +1203,10 @@
       <c r="E24" t="n">
         <v>43</v>
       </c>
-      <c r="F24" t="n">
-        <v>15.6862745098039</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B25" t="n">
         <v>18</v>
@@ -1295,13 +1220,10 @@
       <c r="E25" t="n">
         <v>28</v>
       </c>
-      <c r="F25" t="n">
-        <v>44</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B26" t="n">
         <v>18</v>
@@ -1315,13 +1237,10 @@
       <c r="E26" t="n">
         <v>21</v>
       </c>
-      <c r="F26" t="n">
-        <v>57.1428571428571</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B27" t="n">
         <v>18</v>
@@ -1335,13 +1254,10 @@
       <c r="E27" t="n">
         <v>42</v>
       </c>
-      <c r="F27" t="n">
-        <v>12.5</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B28" t="n">
         <v>18</v>
@@ -1355,13 +1271,10 @@
       <c r="E28" t="n">
         <v>34</v>
       </c>
-      <c r="F28" t="n">
-        <v>22.7272727272727</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B29" t="n">
         <v>18</v>
@@ -1375,13 +1288,10 @@
       <c r="E29" t="n">
         <v>33</v>
       </c>
-      <c r="F29" t="n">
-        <v>23.2558139534884</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B30" t="n">
         <v>18</v>
@@ -1395,13 +1305,10 @@
       <c r="E30" t="n">
         <v>39</v>
       </c>
-      <c r="F30" t="n">
-        <v>2.5</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B31" t="n">
         <v>18</v>
@@ -1415,13 +1322,10 @@
       <c r="E31" t="n">
         <v>31</v>
       </c>
-      <c r="F31" t="n">
-        <v>20.5128205128205</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B32" t="n">
         <v>18</v>
@@ -1435,13 +1339,10 @@
       <c r="E32" t="n">
         <v>29</v>
       </c>
-      <c r="F32" t="n">
-        <v>23.6842105263158</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B33" t="n">
         <v>18</v>
@@ -1455,13 +1356,10 @@
       <c r="E33" t="n">
         <v>27</v>
       </c>
-      <c r="F33" t="n">
-        <v>28.9473684210526</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B34" t="n">
         <v>18</v>
@@ -1475,13 +1373,10 @@
       <c r="E34" t="n">
         <v>26</v>
       </c>
-      <c r="F34" t="n">
-        <v>27.7777777777778</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B35" t="n">
         <v>18</v>
@@ -1495,13 +1390,10 @@
       <c r="E35" t="n">
         <v>23</v>
       </c>
-      <c r="F35" t="n">
-        <v>32.3529411764706</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B36" t="n">
         <v>18</v>
@@ -1515,13 +1407,10 @@
       <c r="E36" t="n">
         <v>21</v>
       </c>
-      <c r="F36" t="n">
-        <v>38.2352941176471</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B37" t="n">
         <v>18</v>
@@ -1535,13 +1424,10 @@
       <c r="E37" t="n">
         <v>30</v>
       </c>
-      <c r="F37" t="n">
-        <v>9.09090909090909</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B38" t="n">
         <v>18</v>
@@ -1555,13 +1441,10 @@
       <c r="E38" t="n">
         <v>23</v>
       </c>
-      <c r="F38" t="n">
-        <v>23.3333333333333</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B39" t="n">
         <v>18</v>
@@ -1575,13 +1458,10 @@
       <c r="E39" t="n">
         <v>21</v>
       </c>
-      <c r="F39" t="n">
-        <v>25</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B40" t="n">
         <v>18</v>
@@ -1595,13 +1475,10 @@
       <c r="E40" t="n">
         <v>17</v>
       </c>
-      <c r="F40" t="n">
-        <v>39.2857142857143</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B41" t="n">
         <v>18</v>
@@ -1615,13 +1492,10 @@
       <c r="E41" t="n">
         <v>20</v>
       </c>
-      <c r="F41" t="n">
-        <v>25.9259259259259</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B42" t="n">
         <v>18</v>
@@ -1635,13 +1509,10 @@
       <c r="E42" t="n">
         <v>26</v>
       </c>
-      <c r="F42" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B43" t="n">
         <v>18</v>
@@ -1655,13 +1526,10 @@
       <c r="E43" t="n">
         <v>21</v>
       </c>
-      <c r="F43" t="n">
-        <v>19.2307692307692</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B44" t="n">
         <v>18</v>
@@ -1675,13 +1543,10 @@
       <c r="E44" t="n">
         <v>20</v>
       </c>
-      <c r="F44" t="n">
-        <v>16.6666666666667</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B45" t="n">
         <v>18</v>
@@ -1695,13 +1560,10 @@
       <c r="E45" t="n">
         <v>18</v>
       </c>
-      <c r="F45" t="n">
-        <v>25</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B46" t="n">
         <v>18</v>
@@ -1715,13 +1577,10 @@
       <c r="E46" t="n">
         <v>17</v>
       </c>
-      <c r="F46" t="n">
-        <v>26.0869565217391</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B47" t="n">
         <v>18</v>
@@ -1735,13 +1594,10 @@
       <c r="E47" t="n">
         <v>19</v>
       </c>
-      <c r="F47" t="n">
-        <v>17.3913043478261</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B48" t="n">
         <v>18</v>
@@ -1755,13 +1611,10 @@
       <c r="E48" t="n">
         <v>18</v>
       </c>
-      <c r="F48" t="n">
-        <v>21.7391304347826</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B49" t="n">
         <v>18</v>
@@ -1775,13 +1628,10 @@
       <c r="E49" t="n">
         <v>12</v>
       </c>
-      <c r="F49" t="n">
-        <v>42.8571428571429</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B50" t="n">
         <v>18</v>
@@ -1795,13 +1645,10 @@
       <c r="E50" t="n">
         <v>19</v>
       </c>
-      <c r="F50" t="n">
-        <v>9.52380952380952</v>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B51" t="n">
         <v>18</v>
@@ -1815,13 +1662,10 @@
       <c r="E51" t="n">
         <v>19</v>
       </c>
-      <c r="F51" t="n">
-        <v>9.52380952380952</v>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B52" t="n">
         <v>18</v>
@@ -1835,13 +1679,10 @@
       <c r="E52" t="n">
         <v>19</v>
       </c>
-      <c r="F52" t="n">
-        <v>9.52380952380952</v>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B53" t="n">
         <v>18</v>
@@ -1855,13 +1696,10 @@
       <c r="E53" t="n">
         <v>14</v>
       </c>
-      <c r="F53" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B54" t="n">
         <v>18</v>
@@ -1875,13 +1713,10 @@
       <c r="E54" t="n">
         <v>13</v>
       </c>
-      <c r="F54" t="n">
-        <v>31.5789473684211</v>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B55" t="n">
         <v>18</v>
@@ -1895,13 +1730,10 @@
       <c r="E55" t="n">
         <v>12</v>
       </c>
-      <c r="F55" t="n">
-        <v>36.8421052631579</v>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B56" t="n">
         <v>18</v>
@@ -1915,13 +1747,10 @@
       <c r="E56" t="n">
         <v>11</v>
       </c>
-      <c r="F56" t="n">
-        <v>38.8888888888889</v>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B57" t="n">
         <v>18</v>
@@ -1935,13 +1764,10 @@
       <c r="E57" t="n">
         <v>16</v>
       </c>
-      <c r="F57" t="n">
-        <v>5.88235294117648</v>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B58" t="n">
         <v>18</v>
@@ -1955,13 +1781,10 @@
       <c r="E58" t="n">
         <v>12</v>
       </c>
-      <c r="F58" t="n">
-        <v>25</v>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B59" t="n">
         <v>18</v>
@@ -1975,13 +1798,10 @@
       <c r="E59" t="n">
         <v>7</v>
       </c>
-      <c r="F59" t="n">
-        <v>56.25</v>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B60" t="n">
         <v>18</v>
@@ -1995,13 +1815,10 @@
       <c r="E60" t="n">
         <v>12</v>
       </c>
-      <c r="F60" t="n">
-        <v>25</v>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B61" t="n">
         <v>18</v>
@@ -2015,13 +1832,10 @@
       <c r="E61" t="n">
         <v>11</v>
       </c>
-      <c r="F61" t="n">
-        <v>26.6666666666667</v>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B62" t="n">
         <v>18</v>
@@ -2035,13 +1849,10 @@
       <c r="E62" t="n">
         <v>9</v>
       </c>
-      <c r="F62" t="n">
-        <v>35.7142857142857</v>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B63" t="n">
         <v>18</v>
@@ -2055,13 +1866,10 @@
       <c r="E63" t="n">
         <v>9</v>
       </c>
-      <c r="F63" t="n">
-        <v>35.7142857142857</v>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B64" t="n">
         <v>18</v>
@@ -2075,13 +1883,10 @@
       <c r="E64" t="n">
         <v>9</v>
       </c>
-      <c r="F64" t="n">
-        <v>35.7142857142857</v>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B65" t="n">
         <v>18</v>
@@ -2095,13 +1900,10 @@
       <c r="E65" t="n">
         <v>9</v>
       </c>
-      <c r="F65" t="n">
-        <v>30.7692307692308</v>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B66" t="n">
         <v>18</v>
@@ -2115,13 +1917,10 @@
       <c r="E66" t="n">
         <v>10</v>
       </c>
-      <c r="F66" t="n">
-        <v>23.0769230769231</v>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B67" t="n">
         <v>18</v>
@@ -2135,13 +1934,10 @@
       <c r="E67" t="n">
         <v>8</v>
       </c>
-      <c r="F67" t="n">
-        <v>33.3333333333333</v>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B68" t="n">
         <v>18</v>
@@ -2155,13 +1951,10 @@
       <c r="E68" t="n">
         <v>6</v>
       </c>
-      <c r="F68" t="n">
-        <v>45.4545454545455</v>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B69" t="n">
         <v>18</v>
@@ -2175,13 +1968,10 @@
       <c r="E69" t="n">
         <v>5</v>
       </c>
-      <c r="F69" t="n">
-        <v>54.5454545454545</v>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B70" t="n">
         <v>18</v>
@@ -2195,13 +1985,10 @@
       <c r="E70" t="n">
         <v>6</v>
       </c>
-      <c r="F70" t="n">
-        <v>45.4545454545455</v>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B71" t="n">
         <v>18</v>
@@ -2215,13 +2002,10 @@
       <c r="E71" t="n">
         <v>7</v>
       </c>
-      <c r="F71" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B72" t="n">
         <v>18</v>
@@ -2235,13 +2019,10 @@
       <c r="E72" t="n">
         <v>6</v>
       </c>
-      <c r="F72" t="n">
-        <v>40</v>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B73" t="n">
         <v>18</v>
@@ -2255,13 +2036,10 @@
       <c r="E73" t="n">
         <v>5</v>
       </c>
-      <c r="F73" t="n">
-        <v>50</v>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B74" t="n">
         <v>18</v>
@@ -2275,13 +2053,10 @@
       <c r="E74" t="n">
         <v>6</v>
       </c>
-      <c r="F74" t="n">
-        <v>40</v>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B75" t="n">
         <v>18</v>
@@ -2295,13 +2070,10 @@
       <c r="E75" t="n">
         <v>3</v>
       </c>
-      <c r="F75" t="n">
-        <v>70</v>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B76" t="n">
         <v>18</v>
@@ -2315,13 +2087,10 @@
       <c r="E76" t="n">
         <v>9</v>
       </c>
-      <c r="F76" t="n">
-        <v>10</v>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B77" t="n">
         <v>18</v>
@@ -2335,13 +2104,10 @@
       <c r="E77" t="n">
         <v>8</v>
       </c>
-      <c r="F77" t="n">
-        <v>20</v>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B78" t="n">
         <v>18</v>
@@ -2355,13 +2121,10 @@
       <c r="E78" t="n">
         <v>6</v>
       </c>
-      <c r="F78" t="n">
-        <v>33.3333333333333</v>
-      </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B79" t="n">
         <v>18</v>
@@ -2375,13 +2138,10 @@
       <c r="E79" t="n">
         <v>6</v>
       </c>
-      <c r="F79" t="n">
-        <v>25</v>
-      </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B80" t="n">
         <v>18</v>
@@ -2395,13 +2155,10 @@
       <c r="E80" t="n">
         <v>5</v>
       </c>
-      <c r="F80" t="n">
-        <v>37.5</v>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B81" t="n">
         <v>18</v>
@@ -2415,13 +2172,10 @@
       <c r="E81" t="n">
         <v>4</v>
       </c>
-      <c r="F81" t="n">
-        <v>42.8571428571429</v>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B82" t="n">
         <v>18</v>
@@ -2435,13 +2189,10 @@
       <c r="E82" t="n">
         <v>4</v>
       </c>
-      <c r="F82" t="n">
-        <v>42.8571428571429</v>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B83" t="n">
         <v>18</v>
@@ -2455,13 +2206,10 @@
       <c r="E83" t="n">
         <v>7</v>
       </c>
-      <c r="F83" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B84" t="n">
         <v>18</v>
@@ -2475,13 +2223,10 @@
       <c r="E84" t="n">
         <v>6</v>
       </c>
-      <c r="F84" t="n">
-        <v>14.2857142857143</v>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B85" t="n">
         <v>18</v>
@@ -2495,13 +2240,10 @@
       <c r="E85" t="n">
         <v>2</v>
       </c>
-      <c r="F85" t="n">
-        <v>71.4285714285714</v>
-      </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B86" t="n">
         <v>18</v>
@@ -2515,13 +2257,10 @@
       <c r="E86" t="n">
         <v>6</v>
       </c>
-      <c r="F86" t="n">
-        <v>14.2857142857143</v>
-      </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B87" t="n">
         <v>18</v>
@@ -2535,13 +2274,10 @@
       <c r="E87" t="n">
         <v>7</v>
       </c>
-      <c r="F87" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B88" t="n">
         <v>18</v>
@@ -2555,13 +2291,10 @@
       <c r="E88" t="n">
         <v>3</v>
       </c>
-      <c r="F88" t="n">
-        <v>50</v>
-      </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B89" t="n">
         <v>18</v>
@@ -2575,13 +2308,10 @@
       <c r="E89" t="n">
         <v>5</v>
       </c>
-      <c r="F89" t="n">
-        <v>16.6666666666667</v>
-      </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B90" t="n">
         <v>18</v>
@@ -2595,13 +2325,10 @@
       <c r="E90" t="n">
         <v>4</v>
       </c>
-      <c r="F90" t="n">
-        <v>33.3333333333333</v>
-      </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B91" t="n">
         <v>18</v>
@@ -2615,13 +2342,10 @@
       <c r="E91" t="n">
         <v>5</v>
       </c>
-      <c r="F91" t="n">
-        <v>16.6666666666667</v>
-      </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B92" t="n">
         <v>18</v>
@@ -2635,13 +2359,10 @@
       <c r="E92" t="n">
         <v>4</v>
       </c>
-      <c r="F92" t="n">
-        <v>33.3333333333333</v>
-      </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B93" t="n">
         <v>18</v>
@@ -2655,13 +2376,10 @@
       <c r="E93" t="n">
         <v>4</v>
       </c>
-      <c r="F93" t="n">
-        <v>33.3333333333333</v>
-      </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B94" t="n">
         <v>18</v>
@@ -2675,13 +2393,10 @@
       <c r="E94" t="n">
         <v>4</v>
       </c>
-      <c r="F94" t="n">
-        <v>20</v>
-      </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B95" t="n">
         <v>18</v>
@@ -2695,13 +2410,10 @@
       <c r="E95" t="n">
         <v>3</v>
       </c>
-      <c r="F95" t="n">
-        <v>40</v>
-      </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B96" t="n">
         <v>18</v>
@@ -2715,13 +2427,10 @@
       <c r="E96" t="n">
         <v>4</v>
       </c>
-      <c r="F96" t="n">
-        <v>20</v>
-      </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B97" t="n">
         <v>18</v>
@@ -2735,13 +2444,10 @@
       <c r="E97" t="n">
         <v>5</v>
       </c>
-      <c r="F97" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B98" t="n">
         <v>18</v>
@@ -2755,13 +2461,10 @@
       <c r="E98" t="n">
         <v>3</v>
       </c>
-      <c r="F98" t="n">
-        <v>40</v>
-      </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B99" t="n">
         <v>18</v>
@@ -2775,13 +2478,10 @@
       <c r="E99" t="n">
         <v>4</v>
       </c>
-      <c r="F99" t="n">
-        <v>20</v>
-      </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B100" t="n">
         <v>18</v>
@@ -2795,13 +2495,10 @@
       <c r="E100" t="n">
         <v>1</v>
       </c>
-      <c r="F100" t="n">
-        <v>80</v>
-      </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B101" t="n">
         <v>18</v>
@@ -2815,13 +2512,10 @@
       <c r="E101" t="n">
         <v>2</v>
       </c>
-      <c r="F101" t="n">
-        <v>60</v>
-      </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B102" t="n">
         <v>18</v>
@@ -2835,13 +2529,10 @@
       <c r="E102" t="n">
         <v>2</v>
       </c>
-      <c r="F102" t="n">
-        <v>60</v>
-      </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B103" t="n">
         <v>18</v>
@@ -2855,13 +2546,10 @@
       <c r="E103" t="n">
         <v>4</v>
       </c>
-      <c r="F103" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B104" t="n">
         <v>18</v>
@@ -2875,13 +2563,10 @@
       <c r="E104" t="n">
         <v>3</v>
       </c>
-      <c r="F104" t="n">
-        <v>25</v>
-      </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B105" t="n">
         <v>18</v>
@@ -2895,13 +2580,10 @@
       <c r="E105" t="n">
         <v>3</v>
       </c>
-      <c r="F105" t="n">
-        <v>25</v>
-      </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B106" t="n">
         <v>18</v>
@@ -2915,13 +2597,10 @@
       <c r="E106" t="n">
         <v>4</v>
       </c>
-      <c r="F106" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B107" t="n">
         <v>18</v>
@@ -2935,13 +2614,10 @@
       <c r="E107" t="n">
         <v>3</v>
       </c>
-      <c r="F107" t="n">
-        <v>25</v>
-      </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B108" t="n">
         <v>18</v>
@@ -2955,13 +2631,10 @@
       <c r="E108" t="n">
         <v>3</v>
       </c>
-      <c r="F108" t="n">
-        <v>25</v>
-      </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B109" t="n">
         <v>18</v>
@@ -2975,13 +2648,10 @@
       <c r="E109" t="n">
         <v>1</v>
       </c>
-      <c r="F109" t="n">
-        <v>75</v>
-      </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B110" t="n">
         <v>18</v>
@@ -2995,13 +2665,10 @@
       <c r="E110" t="n">
         <v>2</v>
       </c>
-      <c r="F110" t="n">
-        <v>33.3333333333333</v>
-      </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B111" t="n">
         <v>18</v>
@@ -3015,13 +2682,10 @@
       <c r="E111" t="n">
         <v>2</v>
       </c>
-      <c r="F111" t="n">
-        <v>33.3333333333333</v>
-      </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B112" t="n">
         <v>18</v>
@@ -3035,13 +2699,10 @@
       <c r="E112" t="n">
         <v>2</v>
       </c>
-      <c r="F112" t="n">
-        <v>33.3333333333333</v>
-      </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B113" t="n">
         <v>18</v>
@@ -3055,13 +2716,10 @@
       <c r="E113" t="n">
         <v>3</v>
       </c>
-      <c r="F113" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B114" t="n">
         <v>18</v>
@@ -3075,13 +2733,10 @@
       <c r="E114" t="n">
         <v>2</v>
       </c>
-      <c r="F114" t="n">
-        <v>33.3333333333333</v>
-      </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B115" t="n">
         <v>18</v>
@@ -3095,13 +2750,10 @@
       <c r="E115" t="n">
         <v>2</v>
       </c>
-      <c r="F115" t="n">
-        <v>33.3333333333333</v>
-      </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B116" t="n">
         <v>18</v>
@@ -3115,13 +2767,10 @@
       <c r="E116" t="n">
         <v>1</v>
       </c>
-      <c r="F116" t="n">
-        <v>66.6666666666667</v>
-      </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B117" t="n">
         <v>18</v>
@@ -3135,13 +2784,10 @@
       <c r="E117" t="n">
         <v>2</v>
       </c>
-      <c r="F117" t="n">
-        <v>33.3333333333333</v>
-      </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B118" t="n">
         <v>18</v>
@@ -3155,13 +2801,10 @@
       <c r="E118" t="n">
         <v>3</v>
       </c>
-      <c r="F118" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B119" t="n">
         <v>18</v>
@@ -3175,13 +2818,10 @@
       <c r="E119" t="n">
         <v>2</v>
       </c>
-      <c r="F119" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B120" t="n">
         <v>18</v>
@@ -3195,13 +2835,10 @@
       <c r="E120" t="n">
         <v>1</v>
       </c>
-      <c r="F120" t="n">
-        <v>50</v>
-      </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B121" t="n">
         <v>18</v>
@@ -3215,13 +2852,10 @@
       <c r="E121" t="n">
         <v>2</v>
       </c>
-      <c r="F121" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B122" t="n">
         <v>18</v>
@@ -3235,13 +2869,10 @@
       <c r="E122" t="n">
         <v>1</v>
       </c>
-      <c r="F122" t="n">
-        <v>50</v>
-      </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B123" t="n">
         <v>18</v>
@@ -3255,13 +2886,10 @@
       <c r="E123" t="n">
         <v>1</v>
       </c>
-      <c r="F123" t="n">
-        <v>50</v>
-      </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B124" t="n">
         <v>18</v>
@@ -3275,13 +2903,10 @@
       <c r="E124" t="n">
         <v>2</v>
       </c>
-      <c r="F124" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B125" t="n">
         <v>18</v>
@@ -3295,13 +2920,10 @@
       <c r="E125" t="n">
         <v>1</v>
       </c>
-      <c r="F125" t="n">
-        <v>50</v>
-      </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B126" t="n">
         <v>18</v>
@@ -3315,13 +2937,10 @@
       <c r="E126" t="n">
         <v>1</v>
       </c>
-      <c r="F126" t="n">
-        <v>50</v>
-      </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B127" t="n">
         <v>18</v>
@@ -3335,13 +2954,10 @@
       <c r="E127" t="n">
         <v>1</v>
       </c>
-      <c r="F127" t="n">
-        <v>50</v>
-      </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B128" t="n">
         <v>18</v>
@@ -3355,13 +2971,10 @@
       <c r="E128" t="n">
         <v>2</v>
       </c>
-      <c r="F128" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B129" t="n">
         <v>18</v>
@@ -3375,13 +2988,10 @@
       <c r="E129" t="n">
         <v>2</v>
       </c>
-      <c r="F129" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B130" t="n">
         <v>18</v>
@@ -3395,13 +3005,10 @@
       <c r="E130" t="n">
         <v>2</v>
       </c>
-      <c r="F130" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B131" t="n">
         <v>18</v>
@@ -3415,13 +3022,10 @@
       <c r="E131" t="n">
         <v>1</v>
       </c>
-      <c r="F131" t="n">
-        <v>50</v>
-      </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B132" t="n">
         <v>18</v>
@@ -3435,13 +3039,10 @@
       <c r="E132" t="n">
         <v>1</v>
       </c>
-      <c r="F132" t="n">
-        <v>50</v>
-      </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B133" t="n">
         <v>18</v>
@@ -3455,13 +3056,10 @@
       <c r="E133" t="n">
         <v>2</v>
       </c>
-      <c r="F133" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B134" t="n">
         <v>18</v>
@@ -3475,13 +3073,10 @@
       <c r="E134" t="n">
         <v>1</v>
       </c>
-      <c r="F134" t="n">
-        <v>50</v>
-      </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B135" t="n">
         <v>18</v>
@@ -3495,13 +3090,10 @@
       <c r="E135" t="n">
         <v>1</v>
       </c>
-      <c r="F135" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B136" t="n">
         <v>18</v>
@@ -3515,13 +3107,10 @@
       <c r="E136" t="n">
         <v>1</v>
       </c>
-      <c r="F136" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B137" t="n">
         <v>18</v>
@@ -3535,13 +3124,10 @@
       <c r="E137" t="n">
         <v>1</v>
       </c>
-      <c r="F137" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B138" t="n">
         <v>18</v>
@@ -3555,13 +3141,10 @@
       <c r="E138" t="n">
         <v>1</v>
       </c>
-      <c r="F138" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B139" t="n">
         <v>18</v>
@@ -3575,13 +3158,10 @@
       <c r="E139" t="n">
         <v>0</v>
       </c>
-      <c r="F139" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B140" t="n">
         <v>18</v>
@@ -3595,13 +3175,10 @@
       <c r="E140" t="n">
         <v>1</v>
       </c>
-      <c r="F140" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B141" t="n">
         <v>18</v>
@@ -3615,13 +3192,10 @@
       <c r="E141" t="n">
         <v>1</v>
       </c>
-      <c r="F141" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B142" t="n">
         <v>18</v>
@@ -3635,13 +3209,10 @@
       <c r="E142" t="n">
         <v>1</v>
       </c>
-      <c r="F142" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B143" t="n">
         <v>18</v>
@@ -3655,13 +3226,10 @@
       <c r="E143" t="n">
         <v>1</v>
       </c>
-      <c r="F143" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B144" t="n">
         <v>18</v>
@@ -3675,13 +3243,10 @@
       <c r="E144" t="n">
         <v>1</v>
       </c>
-      <c r="F144" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B145" t="n">
         <v>18</v>
@@ -3695,13 +3260,10 @@
       <c r="E145" t="n">
         <v>0</v>
       </c>
-      <c r="F145" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B146" t="n">
         <v>18</v>
@@ -3715,13 +3277,10 @@
       <c r="E146" t="n">
         <v>1</v>
       </c>
-      <c r="F146" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B147" t="n">
         <v>18</v>
@@ -3735,13 +3294,10 @@
       <c r="E147" t="n">
         <v>1</v>
       </c>
-      <c r="F147" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B148" t="n">
         <v>18</v>
@@ -3754,9 +3310,6 @@
       </c>
       <c r="E148" t="n">
         <v>1</v>
-      </c>
-      <c r="F148" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3993,13 +3546,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6696F628-C3DF-4EEB-B620-680A27B9752B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE462FBA-4BE9-4B30-91EF-022FB07B35B5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A71D9C4E-D346-4C54-BA62-13F8F1A347C3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91989099-8660-4561-A3B7-FD5036B62BA5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DEB0F8A6-71B2-455D-AE2B-B3B0FB93C21D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8CA8577-8F85-4A99-9B7E-E95DFDCD7544}"/>
 </file>